--- a/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_49.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.2/Output_9_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4645890.57711045</v>
+        <v>4682200.354279869</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13275569.19337385</v>
+        <v>13279501.51514058</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117101935</v>
+        <v>987.0883260128674</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117101935</v>
+        <v>987.0883260128674</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18806456.82317137</v>
+        <v>18805689.90910076</v>
       </c>
     </row>
   </sheetData>
@@ -669,13 +669,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>1.415908396047697</v>
       </c>
       <c r="H2" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1.178257491574186e-12</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,13 +705,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>87.30283556964716</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T2" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U2" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V2" t="n">
         <v>229.8510241668239</v>
@@ -736,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>139.2485741992166</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -748,13 +748,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H3" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,19 +778,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R3" t="n">
-        <v>133.6519859716245</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S3" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T3" t="n">
-        <v>126.6547001872139</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U3" t="n">
-        <v>374</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -845,22 +845,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N4" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O4" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P4" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q4" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675552</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>85.50414770182039</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T5" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U5" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V5" t="n">
         <v>229.8510241668239</v>
@@ -970,16 +970,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>283.7385389488741</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -991,7 +991,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S6" t="n">
-        <v>62.48881128536601</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T6" t="n">
-        <v>4.473444462796863</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U6" t="n">
-        <v>225.2913917698194</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>374</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1082,22 +1082,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N7" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O7" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P7" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q7" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1143,13 +1143,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34732203575993</v>
+        <v>3.343301935257443</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>3.769060713577687</v>
       </c>
       <c r="I8" t="n">
-        <v>1.79868786782652</v>
+        <v>1.953406460791434</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182041</v>
+        <v>85.41253966161941</v>
       </c>
       <c r="T8" t="n">
-        <v>184.8805867536895</v>
+        <v>184.8629887637397</v>
       </c>
       <c r="U8" t="n">
-        <v>249.1884925285102</v>
+        <v>249.1881709204699</v>
       </c>
       <c r="V8" t="n">
         <v>229.8510241668239</v>
@@ -1207,16 +1207,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>259.2948947201913</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1255,16 +1255,16 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>374</v>
+        <v>133.5184388018132</v>
       </c>
       <c r="S9" t="n">
-        <v>374</v>
+        <v>62.44885845517734</v>
       </c>
       <c r="T9" t="n">
-        <v>374</v>
+        <v>4.464774651476091</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>0.1957842884886531</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>106.0748691037268</v>
       </c>
     </row>
     <row r="10">
@@ -1319,22 +1319,22 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>91.79905402550071</v>
+        <v>91.51638189435317</v>
       </c>
       <c r="N10" t="n">
-        <v>143.0380916651276</v>
+        <v>142.7621408454554</v>
       </c>
       <c r="O10" t="n">
-        <v>214.4472689970478</v>
+        <v>214.1923837511461</v>
       </c>
       <c r="P10" t="n">
-        <v>265.2018645413922</v>
+        <v>264.9837661807364</v>
       </c>
       <c r="Q10" t="n">
-        <v>310.437266425598</v>
+        <v>310.286266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>318.3317673254134</v>
+        <v>318.2506853582003</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>40.09991244551929</v>
@@ -1453,7 +1453,7 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>116.6353649945383</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
         <v>18.63624233787687</v>
@@ -1495,19 +1495,19 @@
         <v>501.333570877285</v>
       </c>
       <c r="S12" t="n">
-        <v>131.8202263797057</v>
+        <v>452.8202263797057</v>
       </c>
       <c r="T12" t="n">
-        <v>81.3753501231742</v>
+        <v>402.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>174.1249482875297</v>
       </c>
       <c r="V12" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
         <v>98.86273944538755</v>
@@ -1565,7 +1565,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q13" t="n">
         <v>352.895266425598</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,13 +1617,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H14" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T14" t="n">
         <v>259.6218731858503</v>
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>213.6917283274925</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1732,13 +1732,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S15" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T15" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U15" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V15" t="n">
         <v>93.51066719152016</v>
@@ -1747,7 +1747,7 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>98.86273944538755</v>
+        <v>272.4545553273604</v>
       </c>
       <c r="Y15" t="n">
         <v>78.39139276613435</v>
@@ -1790,25 +1790,25 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M16" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
         <v>155.2579933044718</v>
       </c>
       <c r="O16" t="n">
-        <v>231.765039488851</v>
+        <v>230.9267936392535</v>
       </c>
       <c r="P16" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q16" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>377.7099312598396</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S16" t="n">
         <v>30.56285675203577</v>
@@ -1857,7 +1857,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>73.30747219949504</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T17" t="n">
         <v>259.6218731858503</v>
@@ -1918,19 +1918,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>200.5295027796753</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>3.99961134672543</v>
@@ -1987,7 +1987,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>399.3913927661343</v>
+        <v>251.9832086481071</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>9.483546242607703</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2048,7 +2048,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S19" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>83.36328960686865</v>
       </c>
       <c r="F20" t="n">
-        <v>83.88962870801186</v>
+        <v>84.35021607332619</v>
       </c>
       <c r="G20" t="n">
         <v>81.3744577141519</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C21" t="n">
         <v>40.09991244551929</v>
@@ -2167,13 +2167,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608468</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,7 +2203,7 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>501.333570877285</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
         <v>131.8202263797057</v>
@@ -2221,10 +2221,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>272.4545553273606</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y21" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2319,7 +2319,7 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>89.33915573984979</v>
+        <v>89.79974310516393</v>
       </c>
       <c r="E23" t="n">
         <v>83.36328960686865</v>
@@ -2328,7 +2328,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H23" t="n">
         <v>72.84688483418068</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>142.3350019731772</v>
@@ -2395,22 +2395,22 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D24" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>192.2280582198497</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2443,13 +2443,13 @@
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
@@ -2461,7 +2461,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="25">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,13 +2565,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H26" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4605873653143577</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2632,19 +2632,19 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F27" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H27" t="n">
         <v>325.021973978874</v>
@@ -2674,19 +2674,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
-        <v>356.1325799590961</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T27" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U27" t="n">
-        <v>79.16168051490371</v>
+        <v>382.1025822036418</v>
       </c>
       <c r="V27" t="n">
         <v>93.51066719152016</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2750,16 +2750,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P28" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q28" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S28" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H29" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
         <v>271.2818334606677</v>
       </c>
       <c r="Y29" t="n">
-        <v>190.7780200481207</v>
+        <v>190.3174326828064</v>
       </c>
     </row>
     <row r="30">
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C30" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>3.99961134672543</v>
@@ -2917,7 +2917,7 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
@@ -2926,7 +2926,7 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W30" t="n">
         <v>111.3731429098285</v>
@@ -2935,7 +2935,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>251.9832086481072</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2978,7 +2978,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M31" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N31" t="n">
         <v>155.2579933044718</v>
@@ -2987,7 +2987,7 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>290.5838154131063</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>161.4599003208887</v>
+        <v>160.9993129555745</v>
       </c>
       <c r="C32" t="n">
         <v>128.4745782429939</v>
@@ -3042,7 +3042,7 @@
         <v>81.37445771415189</v>
       </c>
       <c r="H32" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3106,19 +3106,19 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>195.263913103886</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>324.9996113467254</v>
+        <v>177.5914272286984</v>
       </c>
       <c r="H33" t="n">
         <v>4.021973978873961</v>
@@ -3172,7 +3172,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="34">
@@ -3343,7 +3343,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>40.09991244551929</v>
+        <v>213.6917283274924</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -3352,7 +3352,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>113.5995101105026</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>3.999611346725456</v>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>180.333570877285</v>
@@ -3394,7 +3394,7 @@
         <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
         <v>79.16168051490372</v>
@@ -3513,7 +3513,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
@@ -3586,16 +3586,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E39" t="n">
-        <v>195.2639131038856</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G39" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3628,25 +3628,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T39" t="n">
-        <v>402.3753501231742</v>
+        <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V39" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>142.3350019731772</v>
@@ -3814,25 +3814,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>158.5198244189521</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3859,31 +3859,31 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S42" t="n">
-        <v>452.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734933</v>
       </c>
       <c r="W42" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,13 +3987,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4063,13 +4063,13 @@
         <v>21.67209722191262</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>325.021973978874</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4096,31 +4096,31 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>174.1249482875292</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
-        <v>93.51066719152016</v>
+        <v>267.1024830734931</v>
       </c>
       <c r="W45" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4169,16 +4169,16 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O46" t="n">
-        <v>231.765039488851</v>
+        <v>230.9267936392535</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>376.8716854102422</v>
+        <v>377.7099312598395</v>
       </c>
       <c r="S46" t="n">
         <v>30.56285675203577</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106.914147375084</v>
+        <v>104.8416377852028</v>
       </c>
       <c r="C2" t="n">
-        <v>56.9398259175144</v>
+        <v>54.86731632763319</v>
       </c>
       <c r="D2" t="n">
-        <v>46.49623426110047</v>
+        <v>44.42372467121926</v>
       </c>
       <c r="E2" t="n">
-        <v>42.08887102183921</v>
+        <v>40.016361431958</v>
       </c>
       <c r="F2" t="n">
-        <v>37.14985212485754</v>
+        <v>35.07734253497633</v>
       </c>
       <c r="G2" t="n">
-        <v>33.76871875540306</v>
+        <v>33.64713203391805</v>
       </c>
       <c r="H2" t="n">
-        <v>29.92</v>
+        <v>29.84000000000119</v>
       </c>
       <c r="I2" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>399.11</v>
       </c>
       <c r="K2" t="n">
-        <v>327.128108133742</v>
+        <v>694.7957936111288</v>
       </c>
       <c r="L2" t="n">
-        <v>697.388108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="M2" t="n">
-        <v>1067.648108133742</v>
+        <v>1064.065793611129</v>
       </c>
       <c r="N2" t="n">
-        <v>1067.648108133742</v>
+        <v>1433.335793611129</v>
       </c>
       <c r="O2" t="n">
-        <v>1067.648108133742</v>
+        <v>1433.335793611129</v>
       </c>
       <c r="P2" t="n">
-        <v>1125.74</v>
+        <v>1492</v>
       </c>
       <c r="Q2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="S2" t="n">
-        <v>1407.815317606417</v>
+        <v>1405.724707412506</v>
       </c>
       <c r="T2" t="n">
-        <v>1221.067250178448</v>
+        <v>1218.994415731961</v>
       </c>
       <c r="U2" t="n">
-        <v>969.3617021698518</v>
+        <v>967.2891925799706</v>
       </c>
       <c r="V2" t="n">
-        <v>737.1889504861913</v>
+        <v>735.1164408963101</v>
       </c>
       <c r="W2" t="n">
-        <v>496.4076616165473</v>
+        <v>494.3351520266661</v>
       </c>
       <c r="X2" t="n">
-        <v>302.1835874138526</v>
+        <v>300.1110778239714</v>
       </c>
       <c r="Y2" t="n">
-        <v>189.7417362190987</v>
+        <v>187.6692266292175</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>578.2064886541781</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="C3" t="n">
-        <v>578.2064886541781</v>
+        <v>710.9158773809111</v>
       </c>
       <c r="D3" t="n">
-        <v>578.2064886541781</v>
+        <v>570.2607519271569</v>
       </c>
       <c r="E3" t="n">
-        <v>578.2064886541781</v>
+        <v>570.2607519271569</v>
       </c>
       <c r="F3" t="n">
-        <v>578.2064886541781</v>
+        <v>570.2607519271569</v>
       </c>
       <c r="G3" t="n">
-        <v>578.2064886541781</v>
+        <v>241.454702729969</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>241.454702729969</v>
       </c>
       <c r="I3" t="n">
-        <v>33.13396963146437</v>
+        <v>29.84</v>
       </c>
       <c r="J3" t="n">
-        <v>177.6113405614803</v>
+        <v>174.5185557413367</v>
       </c>
       <c r="K3" t="n">
-        <v>401.8775591086939</v>
+        <v>399.1286311753428</v>
       </c>
       <c r="L3" t="n">
-        <v>720.3885386284223</v>
+        <v>714.3818833454036</v>
       </c>
       <c r="M3" t="n">
-        <v>861.5031803712816</v>
+        <v>856.0360750882628</v>
       </c>
       <c r="N3" t="n">
-        <v>1051.274153846774</v>
+        <v>1046.360878846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1341.994549492757</v>
+        <v>1337.587921002191</v>
       </c>
       <c r="P3" t="n">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1345.738421006376</v>
       </c>
       <c r="R3" t="n">
-        <v>1214.459075542376</v>
+        <v>1210.871311105555</v>
       </c>
       <c r="S3" t="n">
-        <v>1151.339064143017</v>
+        <v>1147.791656100326</v>
       </c>
       <c r="T3" t="n">
-        <v>1023.405023549871</v>
+        <v>1143.281782714996</v>
       </c>
       <c r="U3" t="n">
-        <v>645.6272457720935</v>
+        <v>1143.084020807432</v>
       </c>
       <c r="V3" t="n">
-        <v>630.9700061846994</v>
+        <v>1128.426781220038</v>
       </c>
       <c r="W3" t="n">
-        <v>598.2698618313373</v>
+        <v>1095.726636866676</v>
       </c>
       <c r="X3" t="n">
-        <v>578.2064886541781</v>
+        <v>1075.663263689516</v>
       </c>
       <c r="Y3" t="n">
-        <v>578.2064886541781</v>
+        <v>1075.663263689516</v>
       </c>
     </row>
     <row r="4">
@@ -4455,76 +4455,76 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>470.7458303176201</v>
+        <v>332.7348794203497</v>
       </c>
       <c r="C4" t="n">
-        <v>596.7478361360559</v>
+        <v>332.7348794203497</v>
       </c>
       <c r="D4" t="n">
-        <v>710.066980261056</v>
+        <v>446.0540235453498</v>
       </c>
       <c r="E4" t="n">
-        <v>710.066980261056</v>
+        <v>563.8829277567628</v>
       </c>
       <c r="F4" t="n">
-        <v>710.066980261056</v>
+        <v>688.2439003486983</v>
       </c>
       <c r="G4" t="n">
-        <v>710.066980261056</v>
+        <v>841.8343465634524</v>
       </c>
       <c r="H4" t="n">
-        <v>881.2025562401257</v>
+        <v>1012.985795001538</v>
       </c>
       <c r="I4" t="n">
-        <v>881.2025562401257</v>
+        <v>1012.985795001538</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1381.361257449721</v>
       </c>
       <c r="L4" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.387095409585</v>
       </c>
       <c r="M4" t="n">
-        <v>1294.017231267251</v>
+        <v>1292.946305617309</v>
       </c>
       <c r="N4" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.742122945132</v>
       </c>
       <c r="O4" t="n">
-        <v>932.9209073660642</v>
+        <v>932.3861797621563</v>
       </c>
       <c r="P4" t="n">
-        <v>665.0402361121327</v>
+        <v>664.7258098826245</v>
       </c>
       <c r="Q4" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3053387456568</v>
       </c>
       <c r="R4" t="n">
-        <v>29.92</v>
+        <v>29.84</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="T4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="U4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="V4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="W4" t="n">
-        <v>259.1973975316665</v>
+        <v>70.29478771712391</v>
       </c>
       <c r="X4" t="n">
-        <v>358.9884926513279</v>
+        <v>221.3255787413174</v>
       </c>
       <c r="Y4" t="n">
-        <v>358.9884926513279</v>
+        <v>332.7348794203497</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C5" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D5" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E5" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F5" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G5" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K5" t="n">
-        <v>400.18</v>
+        <v>690.7900270351759</v>
       </c>
       <c r="L5" t="n">
-        <v>770.4399999999999</v>
+        <v>755.48</v>
       </c>
       <c r="M5" t="n">
-        <v>770.4399999999999</v>
+        <v>1125.74</v>
       </c>
       <c r="N5" t="n">
-        <v>770.4399999999999</v>
+        <v>1125.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1125.74</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4585,25 +4585,25 @@
         <v>1496</v>
       </c>
       <c r="S5" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T5" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U5" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V5" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W5" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X5" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y5" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>394.6673863086054</v>
+        <v>939.120343254833</v>
       </c>
       <c r="C6" t="n">
-        <v>29.92</v>
+        <v>939.120343254833</v>
       </c>
       <c r="D6" t="n">
-        <v>29.92</v>
+        <v>587.6681342672546</v>
       </c>
       <c r="E6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="F6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="G6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="H6" t="n">
-        <v>29.92</v>
+        <v>241.534702729969</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
       </c>
       <c r="J6" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K6" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L6" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M6" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N6" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O6" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1115.008252590758</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S6" t="n">
-        <v>1051.888241191398</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T6" t="n">
-        <v>1047.369610420896</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U6" t="n">
-        <v>819.8025480271394</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V6" t="n">
-        <v>805.1453084397453</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W6" t="n">
-        <v>772.4451640863832</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X6" t="n">
-        <v>394.6673863086054</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y6" t="n">
-        <v>394.6673863086054</v>
+        <v>1225.724928051676</v>
       </c>
     </row>
     <row r="7">
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>444.5411051194287</v>
+        <v>29.92</v>
       </c>
       <c r="C7" t="n">
-        <v>444.5411051194287</v>
+        <v>29.92</v>
       </c>
       <c r="D7" t="n">
-        <v>557.8602492444288</v>
+        <v>143.2391441250001</v>
       </c>
       <c r="E7" t="n">
-        <v>557.8602492444288</v>
+        <v>261.0680483364131</v>
       </c>
       <c r="F7" t="n">
-        <v>682.2212218363643</v>
+        <v>385.4290209283486</v>
       </c>
       <c r="G7" t="n">
-        <v>789.8745737909392</v>
+        <v>481.6391623681918</v>
       </c>
       <c r="H7" t="n">
-        <v>789.8745737909392</v>
+        <v>652.7906108062779</v>
       </c>
       <c r="I7" t="n">
-        <v>1016.483548464727</v>
+        <v>879.4532726931805</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1249.71327269318</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1381.441257449721</v>
       </c>
       <c r="L7" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M7" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N7" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O7" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P7" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q7" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R7" t="n">
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="U7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="V7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="W7" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="X7" t="n">
-        <v>221.3744667741043</v>
+        <v>29.92</v>
       </c>
       <c r="Y7" t="n">
-        <v>332.7837674531366</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="8">
@@ -4771,46 +4771,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108.731003807232</v>
+        <v>108.8416377852028</v>
       </c>
       <c r="C8" t="n">
-        <v>58.7566823496624</v>
+        <v>58.86731632763319</v>
       </c>
       <c r="D8" t="n">
-        <v>48.31309069324847</v>
+        <v>48.42372467121926</v>
       </c>
       <c r="E8" t="n">
-        <v>43.90572745398721</v>
+        <v>44.016361431958</v>
       </c>
       <c r="F8" t="n">
-        <v>38.96670855700554</v>
+        <v>39.07734253497633</v>
       </c>
       <c r="G8" t="n">
-        <v>35.58557518755106</v>
+        <v>35.70026987310013</v>
       </c>
       <c r="H8" t="n">
-        <v>31.736856432148</v>
+        <v>31.89313783918327</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>30.01969029977264</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>400.2796902997726</v>
       </c>
       <c r="L8" t="n">
-        <v>770.4399999999999</v>
+        <v>696.8157936111288</v>
       </c>
       <c r="M8" t="n">
-        <v>1140.7</v>
+        <v>1067.075793611129</v>
       </c>
       <c r="N8" t="n">
-        <v>1140.7</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="O8" t="n">
-        <v>1437.908108133742</v>
+        <v>1437.335793611129</v>
       </c>
       <c r="P8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1409.632174038565</v>
+        <v>1409.724707412506</v>
       </c>
       <c r="T8" t="n">
-        <v>1222.884106610596</v>
+        <v>1222.994415731961</v>
       </c>
       <c r="U8" t="n">
-        <v>971.1785586019998</v>
+        <v>971.2891925799706</v>
       </c>
       <c r="V8" t="n">
-        <v>739.0058069183393</v>
+        <v>739.1164408963101</v>
       </c>
       <c r="W8" t="n">
-        <v>498.2245180486953</v>
+        <v>498.3351520266661</v>
       </c>
       <c r="X8" t="n">
-        <v>304.0004438460006</v>
+        <v>304.1110778239714</v>
       </c>
       <c r="Y8" t="n">
-        <v>191.5585926512467</v>
+        <v>191.6692266292175</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>291.8340350709004</v>
+        <v>740.8008178458908</v>
       </c>
       <c r="C9" t="n">
-        <v>29.92</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
         <v>29.92</v>
@@ -4874,52 +4874,52 @@
         <v>29.92</v>
       </c>
       <c r="J9" t="n">
-        <v>174.3973709300159</v>
+        <v>174.5985557413367</v>
       </c>
       <c r="K9" t="n">
-        <v>398.6635894772295</v>
+        <v>399.2086311753428</v>
       </c>
       <c r="L9" t="n">
-        <v>717.174568996958</v>
+        <v>718.1819687139391</v>
       </c>
       <c r="M9" t="n">
-        <v>858.2892107398172</v>
+        <v>859.8361604567983</v>
       </c>
       <c r="N9" t="n">
-        <v>1048.06018421531</v>
+        <v>1050.16096421531</v>
       </c>
       <c r="O9" t="n">
-        <v>1338.780579861293</v>
+        <v>1341.388006370727</v>
       </c>
       <c r="P9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1492.786030368536</v>
+        <v>1495.800085368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1115.008252590758</v>
+        <v>1360.932975467714</v>
       </c>
       <c r="S9" t="n">
-        <v>737.23047481298</v>
+        <v>1297.853320462485</v>
       </c>
       <c r="T9" t="n">
-        <v>359.4526970352022</v>
+        <v>1293.343447077155</v>
       </c>
       <c r="U9" t="n">
-        <v>359.2547921888157</v>
+        <v>1293.145685169591</v>
       </c>
       <c r="V9" t="n">
-        <v>344.5975526014216</v>
+        <v>1278.488445582197</v>
       </c>
       <c r="W9" t="n">
-        <v>311.8974082480595</v>
+        <v>1245.788301228835</v>
       </c>
       <c r="X9" t="n">
-        <v>291.8340350709004</v>
+        <v>1225.724928051676</v>
       </c>
       <c r="Y9" t="n">
-        <v>291.8340350709004</v>
+        <v>1118.578595623669</v>
       </c>
     </row>
     <row r="10">
@@ -4929,76 +4929,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>661.1714590309665</v>
+        <v>1021.390962989494</v>
       </c>
       <c r="C10" t="n">
-        <v>787.1734648494023</v>
+        <v>1147.392968807929</v>
       </c>
       <c r="D10" t="n">
-        <v>900.4926089744024</v>
+        <v>1260.712112932929</v>
       </c>
       <c r="E10" t="n">
-        <v>900.4926089744024</v>
+        <v>1378.541017144342</v>
       </c>
       <c r="F10" t="n">
-        <v>1024.853581566338</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="G10" t="n">
-        <v>1024.853581566338</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="J10" t="n">
-        <v>1251.462556240126</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="L10" t="n">
-        <v>1386.743548464727</v>
+        <v>1385.467095409585</v>
       </c>
       <c r="M10" t="n">
-        <v>1294.017231267251</v>
+        <v>1293.026305617309</v>
       </c>
       <c r="N10" t="n">
-        <v>1149.534310393385</v>
+        <v>1148.822122945132</v>
       </c>
       <c r="O10" t="n">
-        <v>932.9209073660642</v>
+        <v>932.4661797621563</v>
       </c>
       <c r="P10" t="n">
-        <v>665.0402361121327</v>
+        <v>664.8058098826245</v>
       </c>
       <c r="Q10" t="n">
-        <v>351.4672397226398</v>
+        <v>351.3853387456568</v>
       </c>
       <c r="R10" t="n">
         <v>29.92</v>
       </c>
       <c r="S10" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>259.1973975316665</v>
+        <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>259.1973975316665</v>
+        <v>276.4812224743522</v>
       </c>
       <c r="V10" t="n">
-        <v>259.1973975316665</v>
+        <v>475.3026153602981</v>
       </c>
       <c r="W10" t="n">
-        <v>431.0883157913439</v>
+        <v>647.1935336199756</v>
       </c>
       <c r="X10" t="n">
-        <v>438.0048206856422</v>
+        <v>798.2243246441691</v>
       </c>
       <c r="Y10" t="n">
-        <v>549.4141213646744</v>
+        <v>909.6336253232014</v>
       </c>
     </row>
     <row r="11">
@@ -5041,10 +5041,10 @@
         <v>1418.446838088717</v>
       </c>
       <c r="M11" t="n">
-        <v>2060.956838088718</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N11" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O11" t="n">
         <v>2399.40799366138</v>
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>264.3753454557945</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C12" t="n">
-        <v>223.8703833896134</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D12" t="n">
-        <v>196.6605986444592</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E12" t="n">
         <v>78.84709864997603</v>
@@ -5138,25 +5138,25 @@
         <v>1658.367018159816</v>
       </c>
       <c r="S12" t="n">
-        <v>1525.215274341931</v>
+        <v>1200.972850099507</v>
       </c>
       <c r="T12" t="n">
-        <v>1443.01795098519</v>
+        <v>794.5331025003411</v>
       </c>
       <c r="U12" t="n">
-        <v>1363.056657535792</v>
+        <v>618.6493163513212</v>
       </c>
       <c r="V12" t="n">
-        <v>1268.601438150418</v>
+        <v>524.1940969659473</v>
       </c>
       <c r="W12" t="n">
-        <v>831.8608897566517</v>
+        <v>411.6959728146054</v>
       </c>
       <c r="X12" t="n">
-        <v>731.9995367815127</v>
+        <v>311.8346198394665</v>
       </c>
       <c r="Y12" t="n">
-        <v>652.8163117652153</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="13">
@@ -5208,13 +5208,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q13" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R13" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C14" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D14" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E14" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F14" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G14" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H14" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I14" t="n">
         <v>51.92</v>
@@ -5278,13 +5278,13 @@
         <v>1418.446838088717</v>
       </c>
       <c r="M14" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N14" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O14" t="n">
-        <v>1579.576939471672</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P14" t="n">
         <v>2009.555081027735</v>
@@ -5296,25 +5296,25 @@
         <v>2596</v>
       </c>
       <c r="S14" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T14" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U14" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V14" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W14" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X14" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y14" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="15">
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>992.2829698086707</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C15" t="n">
-        <v>776.4327391748399</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D15" t="n">
-        <v>749.2229544296857</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E15" t="n">
-        <v>727.3319471348245</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F15" t="n">
-        <v>384.2650356824237</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
         <v>51.92</v>
@@ -5378,7 +5378,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
         <v>1766.721857646244</v>
@@ -5390,10 +5390,10 @@
         <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>1459.907161134389</v>
+        <v>1284.561892566739</v>
       </c>
       <c r="Y15" t="n">
-        <v>1380.723936118092</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="16">
@@ -5436,10 +5436,10 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M16" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N16" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O16" t="n">
         <v>1115.142339091088</v>
@@ -5448,7 +5448,7 @@
         <v>820.7766206439126</v>
       </c>
       <c r="Q16" t="n">
-        <v>464.3167555675509</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R16" t="n">
         <v>82.79157247680381</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C17" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D17" t="n">
-        <v>377.106715382351</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E17" t="n">
-        <v>292.9013723451099</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F17" t="n">
-        <v>208.1643736501484</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G17" t="n">
-        <v>125.9679517166617</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H17" t="n">
         <v>51.92</v>
@@ -5509,13 +5509,13 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K17" t="n">
-        <v>953.2578922784252</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L17" t="n">
+        <v>953.2578922784251</v>
+      </c>
+      <c r="M17" t="n">
         <v>1595.767892278425</v>
-      </c>
-      <c r="M17" t="n">
-        <v>2238.277892278425</v>
       </c>
       <c r="N17" t="n">
         <v>2238.277892278425</v>
@@ -5533,25 +5533,25 @@
         <v>2596</v>
       </c>
       <c r="S17" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T17" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U17" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V17" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W17" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X17" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y17" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="18">
@@ -5561,16 +5561,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>668.040545566246</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C18" t="n">
-        <v>627.5355835000649</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872616</v>
+        <v>424.9805301872615</v>
       </c>
       <c r="E18" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F18" t="n">
         <v>60.0226114399994</v>
@@ -5630,7 +5630,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y18" t="n">
-        <v>1056.481511875667</v>
+        <v>1205.378667550442</v>
       </c>
     </row>
     <row r="19">
@@ -5670,25 +5670,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1609.501360385148</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M19" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N19" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O19" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P19" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q19" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R19" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S19" t="n">
         <v>51.92</v>
@@ -5719,16 +5719,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C20" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D20" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E20" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F20" t="n">
         <v>207.6991338872047</v>
@@ -5746,13 +5746,13 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K20" t="n">
-        <v>737.2059437357115</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L20" t="n">
-        <v>953.2578922784251</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M20" t="n">
-        <v>1595.767892278425</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N20" t="n">
         <v>2238.277892278425</v>
@@ -5767,28 +5767,28 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>492.6952769985969</v>
+        <v>992.2829698086704</v>
       </c>
       <c r="C21" t="n">
-        <v>452.1903149324157</v>
+        <v>951.7780077424893</v>
       </c>
       <c r="D21" t="n">
-        <v>424.9805301872615</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076487</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463099</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5846,28 +5846,28 @@
         <v>2244.187340368535</v>
       </c>
       <c r="R21" t="n">
-        <v>1737.789794027844</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S21" t="n">
-        <v>1604.638050209959</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U21" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1348.024214018445</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>960.319468324315</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y21" t="n">
-        <v>881.1362433080177</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="22">
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C23" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D23" t="n">
         <v>376.6414756194072</v>
@@ -5968,7 +5968,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F23" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G23" t="n">
         <v>125.5027119537179</v>
@@ -5989,13 +5989,13 @@
         <v>1418.446838088717</v>
       </c>
       <c r="M23" t="n">
-        <v>1418.446838088717</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N23" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O23" t="n">
-        <v>2222.086939471673</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P23" t="n">
         <v>2596</v>
@@ -6004,28 +6004,28 @@
         <v>2596</v>
       </c>
       <c r="R23" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S23" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T23" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U23" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W23" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>992.2829698086704</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C24" t="n">
-        <v>627.5355835000651</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D24" t="n">
-        <v>276.0833745124866</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E24" t="n">
-        <v>254.1923672176254</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F24" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6089,7 +6089,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U24" t="n">
         <v>1766.721857646244</v>
@@ -6104,7 +6104,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y24" t="n">
-        <v>1056.481511875667</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C26" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D26" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E26" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F26" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G26" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H26" t="n">
-        <v>52.3852397629438</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I26" t="n">
         <v>51.92</v>
@@ -6220,22 +6220,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>307.5796384907274</v>
+        <v>310.7478922784251</v>
       </c>
       <c r="L26" t="n">
-        <v>523.631587033441</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M26" t="n">
-        <v>1166.141587033441</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>1166.141587033441</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1808.651587033441</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
-        <v>2451.161587033441</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
@@ -6253,16 +6253,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V26" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W26" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X26" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y26" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="27">
@@ -6275,10 +6275,10 @@
         <v>1010.52448325439</v>
       </c>
       <c r="C27" t="n">
-        <v>645.7770969457847</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D27" t="n">
-        <v>618.5673122006306</v>
+        <v>942.8097364430548</v>
       </c>
       <c r="E27" t="n">
         <v>596.6763049057694</v>
@@ -6317,16 +6317,16 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R27" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S27" t="n">
-        <v>1622.879563655678</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T27" t="n">
-        <v>1540.682240298937</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U27" t="n">
         <v>1460.720946849539</v>
@@ -6393,13 +6393,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P28" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R28" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6457,22 +6457,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K29" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L29" t="n">
-        <v>1418.446838088717</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M29" t="n">
-        <v>2060.956838088718</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N29" t="n">
-        <v>2060.956838088718</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O29" t="n">
-        <v>2222.086939471673</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P29" t="n">
-        <v>2418.678945810293</v>
+        <v>2596</v>
       </c>
       <c r="Q29" t="n">
         <v>2596</v>
@@ -6499,7 +6499,7 @@
         <v>951.9859877270223</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="30">
@@ -6509,16 +6509,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>492.6952769985969</v>
+        <v>1141.180125483445</v>
       </c>
       <c r="C30" t="n">
-        <v>452.1903149324157</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872615</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E30" t="n">
-        <v>78.84709864997603</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F30" t="n">
         <v>60.0226114399994</v>
@@ -6560,25 +6560,25 @@
         <v>2062.032218270268</v>
       </c>
       <c r="S30" t="n">
-        <v>1604.638050209959</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U30" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V30" t="n">
-        <v>1023.781789776021</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W30" t="n">
-        <v>911.2836656246791</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X30" t="n">
-        <v>811.4223126495401</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y30" t="n">
-        <v>556.8938190655934</v>
+        <v>1380.723936118091</v>
       </c>
     </row>
     <row r="31">
@@ -6621,13 +6621,13 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M31" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N31" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O31" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
         <v>820.7766206439126</v>
@@ -6667,22 +6667,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C32" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D32" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E32" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F32" t="n">
-        <v>207.6991338872046</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G32" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H32" t="n">
         <v>51.92</v>
@@ -6694,22 +6694,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K32" t="n">
-        <v>775.9368380887173</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L32" t="n">
-        <v>1009.32297330616</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M32" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N32" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O32" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P32" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q32" t="n">
         <v>2596</v>
@@ -6746,19 +6746,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>992.2829698086708</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>627.5355835000655</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D33" t="n">
-        <v>600.3257987549114</v>
+        <v>924.5682229973354</v>
       </c>
       <c r="E33" t="n">
-        <v>403.0895228924003</v>
+        <v>578.4347914600498</v>
       </c>
       <c r="F33" t="n">
-        <v>384.2650356824237</v>
+        <v>235.3678800076489</v>
       </c>
       <c r="G33" t="n">
         <v>55.98259997866057</v>
@@ -6815,7 +6815,7 @@
         <v>1459.907161134389</v>
       </c>
       <c r="Y33" t="n">
-        <v>1056.481511875667</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="34">
@@ -6928,13 +6928,13 @@
         <v>51.92</v>
       </c>
       <c r="J35" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K35" t="n">
-        <v>1009.32297330616</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L35" t="n">
-        <v>1651.83297330616</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M35" t="n">
         <v>1651.83297330616</v>
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>912.8601939406431</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C36" t="n">
-        <v>872.355231874462</v>
+        <v>1100.675163417264</v>
       </c>
       <c r="D36" t="n">
-        <v>520.9030228868835</v>
+        <v>749.2229544296858</v>
       </c>
       <c r="E36" t="n">
-        <v>174.769591349598</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F36" t="n">
         <v>60.02261143999941</v>
@@ -7028,31 +7028,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q36" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R36" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S36" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1443.01795098519</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
-        <v>1363.056657535792</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1268.601438150418</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W36" t="n">
-        <v>1156.103313999076</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X36" t="n">
-        <v>1056.241961023937</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y36" t="n">
-        <v>977.0587360076396</v>
+        <v>1380.723936118092</v>
       </c>
     </row>
     <row r="37">
@@ -7153,7 +7153,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G38" t="n">
         <v>125.5027119537179</v>
@@ -7165,19 +7165,19 @@
         <v>51.92</v>
       </c>
       <c r="J38" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K38" t="n">
-        <v>307.5796384907274</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L38" t="n">
-        <v>523.631587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M38" t="n">
-        <v>1166.141587033441</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N38" t="n">
-        <v>1170.453074689115</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O38" t="n">
         <v>1812.963074689115</v>
@@ -7220,22 +7220,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>668.0405455662462</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C39" t="n">
-        <v>627.5355835000652</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D39" t="n">
-        <v>600.325798754911</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E39" t="n">
-        <v>403.0895228924003</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F39" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H39" t="n">
         <v>51.92</v>
@@ -7274,22 +7274,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1522.440726853217</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U39" t="n">
-        <v>1442.479433403819</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V39" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W39" t="n">
-        <v>1235.526089867103</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X39" t="n">
-        <v>811.4223126495401</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y39" t="n">
-        <v>732.2390876332428</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="40">
@@ -7341,13 +7341,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7408,10 +7408,10 @@
         <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>1418.446838088717</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="M41" t="n">
-        <v>1418.446838088717</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="N41" t="n">
         <v>1651.83297330616</v>
@@ -7426,28 +7426,28 @@
         <v>2596</v>
       </c>
       <c r="R41" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S41" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T41" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U41" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1168.750360872486</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C42" t="n">
-        <v>1128.245398806305</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D42" t="n">
-        <v>776.7931898187261</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E42" t="n">
-        <v>754.9021825238649</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F42" t="n">
-        <v>411.835271071464</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G42" t="n">
-        <v>407.7952596101252</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H42" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="I42" t="n">
-        <v>403.7326596314647</v>
+        <v>51.92</v>
       </c>
       <c r="J42" t="n">
-        <v>596.8967549011032</v>
+        <v>245.0840952696386</v>
       </c>
       <c r="K42" t="n">
-        <v>904.3763400520904</v>
+        <v>552.5636804206258</v>
       </c>
       <c r="L42" t="n">
-        <v>1334.777960137857</v>
+        <v>982.9653005063919</v>
       </c>
       <c r="M42" t="n">
-        <v>1606.463701880716</v>
+        <v>1254.651042249251</v>
       </c>
       <c r="N42" t="n">
-        <v>1930.261603846775</v>
+        <v>1578.44894421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2343.590454775776</v>
+        <v>1991.777795144312</v>
       </c>
       <c r="P42" t="n">
-        <v>2596</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2516.577224131972</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R42" t="n">
-        <v>2334.422102033705</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S42" t="n">
-        <v>1877.027933973396</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T42" t="n">
-        <v>1794.830610616654</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U42" t="n">
-        <v>1714.869317167256</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V42" t="n">
-        <v>1620.414097781882</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W42" t="n">
-        <v>1507.91597363054</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X42" t="n">
-        <v>1408.054620655401</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y42" t="n">
-        <v>1328.871395639104</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="43">
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C44" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D44" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E44" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F44" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G44" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H44" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I44" t="n">
         <v>51.92</v>
@@ -7642,22 +7642,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>775.9368380887173</v>
+        <v>307.5796384907274</v>
       </c>
       <c r="L44" t="n">
-        <v>1418.446838088717</v>
+        <v>523.631587033441</v>
       </c>
       <c r="M44" t="n">
-        <v>1418.446838088717</v>
+        <v>1166.141587033441</v>
       </c>
       <c r="N44" t="n">
-        <v>1651.83297330616</v>
+        <v>1808.651587033441</v>
       </c>
       <c r="O44" t="n">
-        <v>1812.963074689115</v>
+        <v>1969.781688416396</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2166.373694755016</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
@@ -7675,16 +7675,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V44" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W44" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X44" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y44" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="45">
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1141.180125483446</v>
+        <v>168.4528527561725</v>
       </c>
       <c r="C45" t="n">
-        <v>1100.675163417264</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D45" t="n">
-        <v>1073.46537867211</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E45" t="n">
-        <v>1051.574371377249</v>
+        <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>708.507459924848</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>380.2250242210849</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7739,31 +7739,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q45" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R45" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S45" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U45" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V45" t="n">
         <v>1496.92136969322</v>
       </c>
       <c r="W45" t="n">
-        <v>1384.423245541878</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X45" t="n">
-        <v>1284.56189256674</v>
+        <v>636.0770440818908</v>
       </c>
       <c r="Y45" t="n">
-        <v>1205.378667550442</v>
+        <v>232.6513948231691</v>
       </c>
     </row>
     <row r="46">
@@ -7812,13 +7812,13 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076645212</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425881596</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R46" t="n">
         <v>82.79157247680381</v>
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>372.8993027275024</v>
       </c>
       <c r="K2" t="n">
-        <v>248.0502805878618</v>
+        <v>246.0012172915823</v>
       </c>
       <c r="L2" t="n">
-        <v>309.2909949748744</v>
+        <v>307.6565929648241</v>
       </c>
       <c r="M2" t="n">
-        <v>846.2608914614127</v>
+        <v>471.5549969890509</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>776.3653500296342</v>
       </c>
       <c r="O2" t="n">
-        <v>1.159015302735668</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>502.5418702571336</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,7 +8049,7 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L3" t="n">
-        <v>388.0893364597981</v>
+        <v>384.3316744713784</v>
       </c>
       <c r="M3" t="n">
         <v>471.6948204301074</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2405037325275146</v>
+        <v>373.8993027275024</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>240.8741803461754</v>
       </c>
       <c r="L5" t="n">
-        <v>309.2909949748743</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>403.3653500296342</v>
       </c>
       <c r="O5" t="n">
-        <v>301.3692255388387</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>314.7432258698271</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,28 +8438,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>321.3286984924623</v>
       </c>
       <c r="L8" t="n">
-        <v>309.2909949748743</v>
+        <v>234.1880104510425</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>845.554996989051</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>777.3653500296342</v>
       </c>
       <c r="O8" t="n">
-        <v>301.3692255388388</v>
+        <v>0.4816735941929551</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>128.5418702571336</v>
+        <v>128.1077446289929</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8684,13 +8684,13 @@
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>950.4344291498551</v>
+        <v>480.5466050990546</v>
       </c>
       <c r="N11" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O11" t="n">
-        <v>179.1121759491996</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8921,7 +8921,7 @@
         <v>430.7657085427136</v>
       </c>
       <c r="M14" t="n">
-        <v>301.434429149855</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N14" t="n">
         <v>230.4920535472222</v>
@@ -8930,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>235.7435709267094</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9152,16 +9152,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>221.8955197650531</v>
+        <v>3.661228307766578</v>
       </c>
       <c r="L17" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N17" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9389,16 +9389,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>433.9659648939233</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M20" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9632,16 +9632,16 @@
         <v>430.7657085427136</v>
       </c>
       <c r="M23" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>179.1121759491993</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
         <v>23.48346824708341</v>
@@ -9863,25 +9863,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>3.200256351209731</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M26" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O26" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>169.7848954860321</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,16 +10100,16 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L29" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>950.4344291498551</v>
       </c>
       <c r="N29" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,7 +10118,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>202.5956441962828</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,13 +10337,13 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>473.0880804020101</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L32" t="n">
-        <v>17.50927946942295</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N32" t="n">
         <v>879.4920535472222</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,16 +10571,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>278.5269147425628</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L35" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M35" t="n">
-        <v>301.434429149855</v>
+        <v>537.1780000765643</v>
       </c>
       <c r="N35" t="n">
         <v>230.4920535472222</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>60.29262328527625</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N38" t="n">
-        <v>234.8470915832563</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
-        <v>486.2423218353989</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -11051,13 +11051,13 @@
         <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
-        <v>430.7657085427136</v>
+        <v>17.50927946942295</v>
       </c>
       <c r="M41" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>466.2356244739315</v>
+        <v>230.4920535472222</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>466.2356244739315</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>457.4494331410071</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.927393539209746</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -23423,7 +23423,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23651,13 +23651,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8382458495976817</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24836,7 +24836,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -24845,7 +24845,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -25565,7 +25565,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25802,7 +25802,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26027,7 +26027,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -26036,7 +26036,7 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>734756.8010130918</v>
+        <v>734487.1092780824</v>
       </c>
     </row>
     <row r="3">
@@ -26094,7 +26094,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1395929.747187704</v>
+        <v>1395766.8199117</v>
       </c>
     </row>
     <row r="4">
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2057102.693362317</v>
+        <v>2056939.766086313</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2717830.754639224</v>
+        <v>2717750.208863221</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3378993.138916132</v>
+        <v>3378912.593140129</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4040155.523193039</v>
+        <v>4040074.977417035</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4701317.907469943</v>
+        <v>4701237.36169394</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5362480.291746847</v>
+        <v>5362399.745970844</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6023642.676023752</v>
+        <v>6023562.130247748</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6684805.060300657</v>
+        <v>6684724.514524654</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7345967.444577566</v>
+        <v>7345886.898801563</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8007129.828854479</v>
+        <v>8007049.283078476</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8668292.213131392</v>
+        <v>8668211.667355388</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>9329454.597408304</v>
+        <v>9329374.0516323</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9990616.981685216</v>
+        <v>9990536.435909213</v>
       </c>
     </row>
   </sheetData>
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542548.93426342</v>
       </c>
       <c r="C2" t="n">
         <v>1542736.874407429</v>
@@ -26278,7 +26278,7 @@
         <v>1542736.874407429</v>
       </c>
       <c r="E2" t="n">
-        <v>1542712.229979451</v>
+        <v>1542712.22997945</v>
       </c>
       <c r="F2" t="n">
         <v>1542712.229979451</v>
@@ -26287,7 +26287,7 @@
         <v>1542712.22997945</v>
       </c>
       <c r="H2" t="n">
-        <v>1542712.229979451</v>
+        <v>1542712.22997945</v>
       </c>
       <c r="I2" t="n">
         <v>1542712.229979451</v>
@@ -26296,16 +26296,16 @@
         <v>1542712.229979451</v>
       </c>
       <c r="K2" t="n">
-        <v>1542712.229979451</v>
+        <v>1542712.22997945</v>
       </c>
       <c r="L2" t="n">
         <v>1542712.229979452</v>
       </c>
       <c r="M2" t="n">
+        <v>1542712.229979451</v>
+      </c>
+      <c r="N2" t="n">
         <v>1542712.229979452</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1542712.229979451</v>
       </c>
       <c r="O2" t="n">
         <v>1542712.229979451</v>
@@ -26321,16 +26321,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>231098</v>
+        <v>231721</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>589550</v>
+        <v>588575</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,10 +26345,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>388448</v>
+        <v>388096</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570823.1065049332</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568738.1032495913</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634526</v>
+        <v>566727.0147207876</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.9797961749</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457891</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308644</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468216.2325286012</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.4934089099</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26425,13 +26425,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58590.39999999999</v>
+        <v>58551.39999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="D5" t="n">
-        <v>58590.39999999999</v>
+        <v>58612.2</v>
       </c>
       <c r="E5" t="n">
         <v>73944.549</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>675583.5397406638</v>
+        <v>681453.4277584871</v>
       </c>
       <c r="C6" t="n">
-        <v>908690.4619281526</v>
+        <v>915034.5711578375</v>
       </c>
       <c r="D6" t="n">
-        <v>910702.1093439766</v>
+        <v>917397.6596866414</v>
       </c>
       <c r="E6" t="n">
-        <v>389278.7011832757</v>
+        <v>396716.6923136297</v>
       </c>
       <c r="F6" t="n">
-        <v>980514.764001499</v>
+        <v>986977.7551318529</v>
       </c>
       <c r="G6" t="n">
-        <v>982203.1535231514</v>
+        <v>988666.1446535055</v>
       </c>
       <c r="H6" t="n">
-        <v>983893.8864331142</v>
+        <v>990356.8775634681</v>
       </c>
       <c r="I6" t="n">
-        <v>985586.9796336616</v>
+        <v>992049.9707640164</v>
       </c>
       <c r="J6" t="n">
-        <v>598834.4502485861</v>
+        <v>605649.4413789411</v>
       </c>
       <c r="K6" t="n">
-        <v>988980.3156274195</v>
+        <v>995091.3067577734</v>
       </c>
       <c r="L6" t="n">
-        <v>990680.5933497645</v>
+        <v>997143.5844801186</v>
       </c>
       <c r="M6" t="n">
-        <v>895583.3012297322</v>
+        <v>902046.2923600862</v>
       </c>
       <c r="N6" t="n">
-        <v>994088.4573204952</v>
+        <v>1000551.44845085</v>
       </c>
       <c r="O6" t="n">
-        <v>738996.0799189573</v>
+        <v>745459.0710493121</v>
       </c>
       <c r="P6" t="n">
-        <v>997506.1875705413</v>
+        <v>1003969.178700895</v>
       </c>
     </row>
   </sheetData>
@@ -26807,13 +26807,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="n">
         <v>344</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
         <v>374</v>
@@ -27002,13 +27002,13 @@
         <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>321</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27033,7 +27033,7 @@
         <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" t="n">
         <v>-0</v>
@@ -27076,10 +27076,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
         <v>-0</v>
@@ -27100,10 +27100,10 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>-0</v>
@@ -27317,10 +27317,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>134.2726973711268</v>
+        <v>134.1177124465025</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S2" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,10 +27515,10 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>208.689112698486</v>
       </c>
       <c r="E3" t="n">
         <v>342.6720972219126</v>
@@ -27527,10 +27527,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27566,10 +27566,10 @@
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>277.818744275583</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>26.1959257979226</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27591,34 +27591,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>171.1020457840527</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J4" t="n">
-        <v>396.2647849014816</v>
+        <v>394.2337198135388</v>
       </c>
       <c r="K4" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27645,10 +27645,10 @@
         <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V4" t="n">
         <v>199.1703102162162</v>
@@ -27657,10 +27657,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>348.2427314095635</v>
+        <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321735</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S5" t="n">
         <v>400</v>
@@ -27749,28 +27749,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>100.8180176974525</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,7 +27806,7 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>174.9045340281032</v>
+        <v>400</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>45.86273944538755</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27828,7 +27828,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
         <v>272.7252466480447</v>
@@ -27837,28 +27837,28 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>353.6006979653762</v>
+        <v>342.0400961869587</v>
       </c>
       <c r="H7" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>396.1372930982029</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>359.1365780635112</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>209.2309599488807</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>150.9482601269169</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27894,10 +27894,10 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>132.4740095033003</v>
+        <v>132.1643059857123</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>225.120779732817</v>
+        <v>224.8682520946261</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>101.805017725328</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>325.517988705216</v>
       </c>
       <c r="H9" t="n">
-        <v>330.0491815260438</v>
+        <v>330.0284079411381</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>209.4985557026693</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,16 +28031,16 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>144.7989632036872</v>
       </c>
       <c r="R9" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>30.47344446279683</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>293.3165236624076</v>
       </c>
     </row>
     <row r="10">
@@ -28074,28 +28074,28 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>281.3788946195025</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>244.858135136612</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>227.1197490524383</v>
       </c>
       <c r="I10" t="n">
-        <v>400</v>
+        <v>171.047816275856</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>22.13729309820286</v>
       </c>
       <c r="K10" t="n">
-        <v>400</v>
+        <v>266.941429538848</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>395.9334970102382</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>359.1365780635112</v>
+      </c>
+      <c r="T10" t="n">
+        <v>209.2309599488807</v>
+      </c>
+      <c r="U10" t="n">
         <v>400</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>400</v>
-      </c>
-      <c r="U10" t="n">
-        <v>150.9483584875727</v>
-      </c>
-      <c r="V10" t="n">
-        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
       </c>
       <c r="X10" t="n">
-        <v>254.4300140102068</v>
+        <v>400</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C12" t="n">
         <v>321</v>
@@ -28232,7 +28232,7 @@
         <v>321</v>
       </c>
       <c r="E12" t="n">
-        <v>226.0367322273743</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
         <v>321</v>
@@ -28274,19 +28274,19 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>226.036732227374</v>
       </c>
       <c r="V12" t="n">
         <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
         <v>321</v>
@@ -28402,7 +28402,7 @@
         <v>321</v>
       </c>
       <c r="I14" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28432,7 +28432,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S14" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T14" t="n">
         <v>321</v>
@@ -28460,22 +28460,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C15" t="n">
-        <v>147.4081841180268</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
         <v>321</v>
@@ -28526,7 +28526,7 @@
         <v>321</v>
       </c>
       <c r="X15" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="Y15" t="n">
         <v>321</v>
@@ -28636,7 +28636,7 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="I17" t="n">
         <v>96.76634561233286</v>
@@ -28669,7 +28669,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S17" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T17" t="n">
         <v>321</v>
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>147.4081841180273</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G18" t="n">
         <v>321</v>
@@ -28766,7 +28766,7 @@
         <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>147.4081841180273</v>
       </c>
     </row>
     <row r="19">
@@ -28867,7 +28867,7 @@
         <v>321</v>
       </c>
       <c r="F20" t="n">
-        <v>321</v>
+        <v>320.5394126346857</v>
       </c>
       <c r="G20" t="n">
         <v>321</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C21" t="n">
         <v>321</v>
@@ -28946,13 +28946,13 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
       </c>
       <c r="H21" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="I21" t="n">
         <v>191.6509141932353</v>
@@ -28982,7 +28982,7 @@
         <v>78.62854810934749</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="S21" t="n">
         <v>321</v>
@@ -29000,10 +29000,10 @@
         <v>321</v>
       </c>
       <c r="X21" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="Y21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -29098,7 +29098,7 @@
         <v>321</v>
       </c>
       <c r="D23" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="E23" t="n">
         <v>321</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S23" t="n">
         <v>321</v>
@@ -29174,16 +29174,16 @@
         <v>321</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>147.4081841180271</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>321</v>
@@ -29240,7 +29240,7 @@
         <v>321</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25">
@@ -29350,7 +29350,7 @@
         <v>321</v>
       </c>
       <c r="I26" t="n">
-        <v>96.3057582470185</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29411,13 +29411,13 @@
         <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D27" t="n">
         <v>321</v>
       </c>
       <c r="E27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>321</v>
@@ -29453,19 +29453,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
         <v>321</v>
       </c>
       <c r="S27" t="n">
-        <v>96.6876464206095</v>
+        <v>321</v>
       </c>
       <c r="T27" t="n">
         <v>321</v>
       </c>
       <c r="U27" t="n">
-        <v>321</v>
+        <v>18.05909831126189</v>
       </c>
       <c r="V27" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29635,7 +29635,7 @@
         <v>321</v>
       </c>
       <c r="Y29" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30">
@@ -29645,19 +29645,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C30" t="n">
         <v>321</v>
       </c>
       <c r="D30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>321</v>
@@ -29696,7 +29696,7 @@
         <v>321</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T30" t="n">
         <v>321</v>
@@ -29705,7 +29705,7 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W30" t="n">
         <v>321</v>
@@ -29714,7 +29714,7 @@
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>147.4081841180272</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29803,25 +29803,25 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>321</v>
+      </c>
+      <c r="C32" t="n">
+        <v>321</v>
+      </c>
+      <c r="D32" t="n">
+        <v>321</v>
+      </c>
+      <c r="E32" t="n">
+        <v>321</v>
+      </c>
+      <c r="F32" t="n">
+        <v>321</v>
+      </c>
+      <c r="G32" t="n">
+        <v>321</v>
+      </c>
+      <c r="H32" t="n">
         <v>320.5394126346858</v>
-      </c>
-      <c r="C32" t="n">
-        <v>321</v>
-      </c>
-      <c r="D32" t="n">
-        <v>321</v>
-      </c>
-      <c r="E32" t="n">
-        <v>321</v>
-      </c>
-      <c r="F32" t="n">
-        <v>321</v>
-      </c>
-      <c r="G32" t="n">
-        <v>321</v>
-      </c>
-      <c r="H32" t="n">
-        <v>321</v>
       </c>
       <c r="I32" t="n">
         <v>96.76634561233286</v>
@@ -29885,19 +29885,19 @@
         <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>147.4081841180266</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>147.408184118027</v>
       </c>
       <c r="H33" t="n">
         <v>321</v>
@@ -29951,7 +29951,7 @@
         <v>321</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="34">
@@ -30122,7 +30122,7 @@
         <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>321</v>
+        <v>147.4081841180269</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -30131,7 +30131,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>226.0367322273743</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
@@ -30164,7 +30164,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R36" t="n">
         <v>321</v>
@@ -30173,7 +30173,7 @@
         <v>321</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U36" t="n">
         <v>321</v>
@@ -30365,10 +30365,10 @@
         <v>321</v>
       </c>
       <c r="E39" t="n">
-        <v>147.408184118027</v>
+        <v>321</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G39" t="n">
         <v>321</v>
@@ -30410,22 +30410,22 @@
         <v>321</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="U39" t="n">
         <v>321</v>
       </c>
       <c r="V39" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S41" t="n">
         <v>321</v>
@@ -30593,19 +30593,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>226.0367322273745</v>
+        <v>321</v>
       </c>
       <c r="C42" t="n">
         <v>321</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E42" t="n">
         <v>321</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G42" t="n">
         <v>321</v>
@@ -30638,13 +30638,13 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
         <v>321</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="T42" t="n">
         <v>321</v>
@@ -30653,16 +30653,16 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="W42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -30769,10 +30769,10 @@
         <v>321</v>
       </c>
       <c r="H44" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I44" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30842,13 +30842,13 @@
         <v>321</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="I45" t="n">
         <v>191.6509141932353</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R45" t="n">
         <v>321</v>
@@ -30887,19 +30887,19 @@
         <v>321</v>
       </c>
       <c r="U45" t="n">
-        <v>226.0367322273745</v>
+        <v>321</v>
       </c>
       <c r="V45" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="W45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -31091,49 +31091,49 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H2" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I2" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J2" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L2" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M2" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N2" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O2" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P2" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q2" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R2" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S2" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T2" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U2" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -31170,49 +31170,49 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H3" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I3" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J3" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K3" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M3" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O3" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P3" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q3" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R3" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S3" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -31249,49 +31249,49 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H4" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I4" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K4" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L4" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M4" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N4" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O4" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P4" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q4" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R4" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S4" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T4" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -31328,49 +31328,49 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H5" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I5" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J5" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K5" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M5" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N5" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O5" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P5" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q5" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R5" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S5" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T5" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U5" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -31407,49 +31407,49 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H6" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I6" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J6" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K6" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M6" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O6" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P6" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q6" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R6" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S6" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -31486,49 +31486,49 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H7" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I7" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J7" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K7" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L7" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M7" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N7" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O7" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P7" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R7" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S7" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T7" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -31565,49 +31565,49 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4100502512562811</v>
+        <v>0.4140703517587936</v>
       </c>
       <c r="H8" t="n">
-        <v>4.199427135678389</v>
+        <v>4.240597989949746</v>
       </c>
       <c r="I8" t="n">
-        <v>15.80846231155779</v>
+        <v>15.96344723618091</v>
       </c>
       <c r="J8" t="n">
-        <v>34.80250251256282</v>
+        <v>35.14370351758794</v>
       </c>
       <c r="K8" t="n">
-        <v>52.15992964824121</v>
+        <v>52.67130150753769</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>65.34340703517589</v>
       </c>
       <c r="M8" t="n">
-        <v>72.00123618090453</v>
+        <v>72.70713065326633</v>
       </c>
       <c r="N8" t="n">
-        <v>73.16629145728643</v>
+        <v>73.88360804020101</v>
       </c>
       <c r="O8" t="n">
-        <v>69.08885427135678</v>
+        <v>69.76619597989949</v>
       </c>
       <c r="P8" t="n">
-        <v>58.96573869346734</v>
+        <v>59.54383417085427</v>
       </c>
       <c r="Q8" t="n">
-        <v>44.28081407035176</v>
+        <v>44.71493969849246</v>
       </c>
       <c r="R8" t="n">
-        <v>25.75781909547739</v>
+        <v>26.01034673366835</v>
       </c>
       <c r="S8" t="n">
-        <v>9.344020100502515</v>
+        <v>9.435628140703519</v>
       </c>
       <c r="T8" t="n">
-        <v>1.794994974874371</v>
+        <v>1.81259296482412</v>
       </c>
       <c r="U8" t="n">
-        <v>0.03280402010050248</v>
+        <v>0.03312562814070349</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -31644,49 +31644,49 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2193962264150943</v>
+        <v>0.2215471698113208</v>
       </c>
       <c r="H9" t="n">
-        <v>2.118905660377359</v>
+        <v>2.139679245283019</v>
       </c>
       <c r="I9" t="n">
-        <v>7.553773584905661</v>
+        <v>7.627830188679247</v>
       </c>
       <c r="J9" t="n">
-        <v>20.7281320754717</v>
+        <v>20.93134905660378</v>
       </c>
       <c r="K9" t="n">
-        <v>35.42767924528302</v>
+        <v>35.77500943396227</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63688679245283</v>
+        <v>48.10391509433963</v>
       </c>
       <c r="M9" t="n">
-        <v>55.58999999999999</v>
+        <v>56.13499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>57.06130188679246</v>
+        <v>57.62072641509435</v>
       </c>
       <c r="O9" t="n">
-        <v>52.19994339622642</v>
+        <v>52.71170754716981</v>
       </c>
       <c r="P9" t="n">
-        <v>41.89505660377359</v>
+        <v>42.3057924528302</v>
       </c>
       <c r="Q9" t="n">
-        <v>28.00573584905661</v>
+        <v>28.28030188679246</v>
       </c>
       <c r="R9" t="n">
-        <v>13.62181132075472</v>
+        <v>13.75535849056604</v>
       </c>
       <c r="S9" t="n">
-        <v>4.07518867924528</v>
+        <v>4.115141509433959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843207547169808</v>
+        <v>0.8929905660377355</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01443396226415095</v>
+        <v>0.01457547169811321</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -31723,49 +31723,49 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1839344262295082</v>
+        <v>0.1857377049180328</v>
       </c>
       <c r="H10" t="n">
-        <v>1.635344262295083</v>
+        <v>1.651377049180329</v>
       </c>
       <c r="I10" t="n">
-        <v>5.531409836065575</v>
+        <v>5.585639344262296</v>
       </c>
       <c r="J10" t="n">
-        <v>13.00416393442623</v>
+        <v>13.13165573770492</v>
       </c>
       <c r="K10" t="n">
-        <v>21.36983606557376</v>
+        <v>21.57934426229507</v>
       </c>
       <c r="L10" t="n">
-        <v>27.34603278688525</v>
+        <v>27.61413114754098</v>
       </c>
       <c r="M10" t="n">
-        <v>28.83255737704917</v>
+        <v>29.11522950819672</v>
       </c>
       <c r="N10" t="n">
-        <v>28.1469836065574</v>
+        <v>28.42293442622952</v>
       </c>
       <c r="O10" t="n">
-        <v>25.99829508196722</v>
+        <v>26.25318032786886</v>
       </c>
       <c r="P10" t="n">
-        <v>22.24603278688523</v>
+        <v>22.46413114754097</v>
       </c>
       <c r="Q10" t="n">
-        <v>15.402</v>
+        <v>15.553</v>
       </c>
       <c r="R10" t="n">
-        <v>8.270360655737703</v>
+        <v>8.351442622950817</v>
       </c>
       <c r="S10" t="n">
-        <v>3.205475409836064</v>
+        <v>3.236901639344261</v>
       </c>
       <c r="T10" t="n">
-        <v>0.785901639344262</v>
+        <v>0.7936065573770489</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01003278688524591</v>
+        <v>0.01013114754098362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="K2" t="n">
-        <v>300.210210236103</v>
+        <v>298.67251879912</v>
       </c>
       <c r="L2" t="n">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="M2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>373</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34822,25 +34822,25 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K3" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L3" t="n">
-        <v>321.7282621411399</v>
+        <v>318.4376284546069</v>
       </c>
       <c r="M3" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N3" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O3" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P3" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -34877,37 +34877,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>155.141864863388</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>372.096426715336</v>
       </c>
       <c r="K4" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>40.86342193648881</v>
       </c>
       <c r="T4" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -34943,10 +34943,10 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>100.799085979456</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K5" t="n">
+        <v>293.5454818537131</v>
+      </c>
+      <c r="L5" t="n">
+        <v>65.34340703517591</v>
+      </c>
+      <c r="M5" t="n">
         <v>374</v>
       </c>
-      <c r="L5" t="n">
-        <v>373.9999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>300.2102102361031</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>374</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35059,25 +35059,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K6" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L6" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M6" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N6" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O6" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P6" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -35114,7 +35114,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -35123,28 +35123,28 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>108.7407595500756</v>
+        <v>97.18196105034673</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8802509475617</v>
       </c>
       <c r="I7" t="n">
-        <v>228.8979542159473</v>
+        <v>228.952183724144</v>
       </c>
       <c r="J7" t="n">
         <v>374</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>133.058570461152</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.06650298976183</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35180,10 +35180,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,25 +35217,25 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.1006972724976123</v>
       </c>
       <c r="K8" t="n">
         <v>374</v>
       </c>
       <c r="L8" t="n">
-        <v>373.9999999999999</v>
+        <v>299.5314174862184</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>300.2102102361032</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>58.67867865278593</v>
+        <v>59.25677413017286</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35296,25 +35296,25 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>145.9367383131474</v>
+        <v>146.1399552942795</v>
       </c>
       <c r="K9" t="n">
-        <v>226.5315338860743</v>
+        <v>226.8788640747536</v>
       </c>
       <c r="L9" t="n">
-        <v>321.7282621411399</v>
+        <v>322.1952904430266</v>
       </c>
       <c r="M9" t="n">
-        <v>142.5400421645043</v>
+        <v>143.0850421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>191.6878519954473</v>
+        <v>192.2472765237492</v>
       </c>
       <c r="O9" t="n">
-        <v>293.6569652989728</v>
+        <v>294.1687294499162</v>
       </c>
       <c r="P9" t="n">
-        <v>155.5610611184268</v>
+        <v>155.9717969674834</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -35360,10 +35360,10 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>6.996038651760555</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35372,16 +35372,16 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>228.8979542159473</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>132.8490622644307</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190.7613351330866</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0517398730831</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>6.986368580099263</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35463,13 +35463,13 @@
         <v>649</v>
       </c>
       <c r="M11" t="n">
+        <v>179.1121759491996</v>
+      </c>
+      <c r="N11" t="n">
         <v>649</v>
       </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
       <c r="O11" t="n">
-        <v>341.8698541138006</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P11" t="n">
         <v>198.5777841804241</v>
@@ -35700,7 +35700,7 @@
         <v>649</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -35709,7 +35709,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P14" t="n">
-        <v>434.3213551071335</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q14" t="n">
         <v>592.3686050224903</v>
@@ -35843,7 +35843,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H16" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I16" t="n">
         <v>163.0214951995539</v>
@@ -35931,16 +35931,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K17" t="n">
-        <v>397.807439363043</v>
+        <v>179.5731479057565</v>
       </c>
       <c r="L17" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
         <v>649</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O17" t="n">
         <v>162.757678164601</v>
@@ -36168,16 +36168,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K20" t="n">
-        <v>609.8778844919133</v>
+        <v>649</v>
       </c>
       <c r="L20" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M20" t="n">
         <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O20" t="n">
         <v>162.757678164601</v>
@@ -36411,16 +36411,16 @@
         <v>649</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P23" t="n">
-        <v>377.6899601296234</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,25 +36642,25 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>179.1121759491997</v>
       </c>
       <c r="L26" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M26" t="n">
         <v>649</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O26" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P26" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>146.3014272389487</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36791,7 +36791,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H28" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I28" t="n">
         <v>163.0214951995539</v>
@@ -36879,16 +36879,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K29" t="n">
-        <v>649</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L29" t="n">
-        <v>649</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
         <v>649</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O29" t="n">
         <v>162.757678164601</v>
@@ -36897,7 +36897,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q29" t="n">
-        <v>179.1121759491994</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37116,13 +37116,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K32" t="n">
+        <v>609.8778844919133</v>
+      </c>
+      <c r="L32" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M32" t="n">
         <v>649</v>
-      </c>
-      <c r="L32" t="n">
-        <v>235.7435709267094</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>649</v>
@@ -37134,7 +37134,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,16 +37350,16 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K35" t="n">
-        <v>454.4388343405527</v>
+        <v>649</v>
       </c>
       <c r="L35" t="n">
         <v>649</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>235.7435709267093</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K38" t="n">
         <v>175.9119195979899</v>
       </c>
       <c r="L38" t="n">
-        <v>218.2342914572864</v>
+        <v>278.5269147425627</v>
       </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>649</v>
       </c>
-      <c r="N38" t="n">
-        <v>4.355038036034114</v>
-      </c>
       <c r="O38" t="n">
-        <v>649</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P38" t="n">
         <v>198.5777841804241</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37830,13 +37830,13 @@
         <v>649</v>
       </c>
       <c r="L41" t="n">
+        <v>235.7435709267094</v>
+      </c>
+      <c r="M41" t="n">
         <v>649</v>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
-        <v>235.7435709267093</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38064,16 +38064,16 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
+        <v>175.9119195979899</v>
+      </c>
+      <c r="L44" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M44" t="n">
         <v>649</v>
       </c>
-      <c r="L44" t="n">
+      <c r="N44" t="n">
         <v>649</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>235.7435709267093</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
@@ -38082,7 +38082,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>433.9659648939237</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,7 +38213,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
